--- a/artfynd/A 1861-2024 artfynd.xlsx
+++ b/artfynd/A 1861-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1861-2024 artfynd.xlsx
+++ b/artfynd/A 1861-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1851,6 +1851,127 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122726264</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79776</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kullen nord Ekhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>478348</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6363056</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sävsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På vindfällena aspar i avverkade ytan....</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Robin Isaksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1861-2024 artfynd.xlsx
+++ b/artfynd/A 1861-2024 artfynd.xlsx
@@ -1856,7 +1856,7 @@
         <v>122726264</v>
       </c>
       <c r="B12" t="n">
-        <v>79776</v>
+        <v>79878</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 1861-2024 artfynd.xlsx
+++ b/artfynd/A 1861-2024 artfynd.xlsx
@@ -1856,7 +1856,7 @@
         <v>122726264</v>
       </c>
       <c r="B12" t="n">
-        <v>79878</v>
+        <v>79882</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 1861-2024 artfynd.xlsx
+++ b/artfynd/A 1861-2024 artfynd.xlsx
@@ -1856,7 +1856,7 @@
         <v>122726264</v>
       </c>
       <c r="B12" t="n">
-        <v>79882</v>
+        <v>79885</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 1861-2024 artfynd.xlsx
+++ b/artfynd/A 1861-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1429,7 +1429,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115221641</v>
+        <v>115221625</v>
       </c>
       <c r="B8" t="n">
         <v>79518</v>
@@ -1468,17 +1468,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kullen nord Ekhagen, Sm</t>
+          <t>N Sävsjö, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478348</v>
+        <v>478272</v>
       </c>
       <c r="R8" t="n">
-        <v>6363056</v>
+        <v>6363082</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115221625</v>
+        <v>115221639</v>
       </c>
       <c r="B9" t="n">
         <v>79518</v>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478272</v>
+        <v>478330</v>
       </c>
       <c r="R9" t="n">
-        <v>6363082</v>
+        <v>6363054</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115221639</v>
+        <v>115221621</v>
       </c>
       <c r="B10" t="n">
-        <v>79518</v>
+        <v>78882</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1657,21 +1657,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6431</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478330</v>
+        <v>478272</v>
       </c>
       <c r="R10" t="n">
-        <v>6363054</v>
+        <v>6363082</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115221621</v>
+        <v>122726264</v>
       </c>
       <c r="B11" t="n">
-        <v>78882</v>
+        <v>79885</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6431</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,17 +1786,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Sävsjö, Sm</t>
+          <t>Kullen nord Ekhagen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478272</v>
+        <v>478348</v>
       </c>
       <c r="R11" t="n">
-        <v>6363082</v>
+        <v>6363056</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,12 +1820,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2025-02-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På vindfällena aspar i avverkade ytan....</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,6 +1843,16 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1850,127 +1865,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>122726264</v>
-      </c>
-      <c r="B12" t="n">
-        <v>79885</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6463</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Bårdlav</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Kullen nord Ekhagen, Sm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>478348</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6363056</v>
-      </c>
-      <c r="S12" t="n">
-        <v>25</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Sävsjö</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Sävsjö</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På vindfällena aspar i avverkade ytan....</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Robin Isaksson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Robin Isaksson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
